--- a/artfynd/A 15592-2022 artfynd.xlsx
+++ b/artfynd/A 15592-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15592-2022 artfynd.xlsx
+++ b/artfynd/A 15592-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87278035</v>
+        <v>87278025</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,24 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -716,7 +715,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -727,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>642005.3057247528</v>
+        <v>642005</v>
       </c>
       <c r="R2" t="n">
-        <v>6702389.556002702</v>
+        <v>6702390</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +759,9 @@
           <t>2020-08-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-08-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,15 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>87278078</v>
+        <v>87278252</v>
       </c>
       <c r="B3" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,24 +810,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -851,7 +839,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -862,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>642005.3057247528</v>
+        <v>641935</v>
       </c>
       <c r="R3" t="n">
-        <v>6702389.556002702</v>
+        <v>6702460</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,19 +883,9 @@
           <t>2020-08-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-08-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,16 +897,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Skogsplantering med "halvhöga!" granar på dikad mark.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -945,15 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87278025</v>
+        <v>87278078</v>
       </c>
       <c r="B4" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,28 +924,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -990,7 +949,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -1001,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>642005.3057247528</v>
+        <v>642005</v>
       </c>
       <c r="R4" t="n">
-        <v>6702389.556002702</v>
+        <v>6702390</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1034,19 +993,9 @@
           <t>2020-08-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-08-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1081,6 +1030,126 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>87278035</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nyängen 2,4 km SV om Västlands kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>642005</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6702390</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-08-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-08-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Ängsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Skogsplantering med "halvhöga!" granar på dikad mark.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15592-2022 artfynd.xlsx
+++ b/artfynd/A 15592-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87278025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87278252</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,6 +1045,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87278078</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1150,8 +1170,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87278035</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>